--- a/output/bkg pending - ICD LKT - Esco Ladkrabang (GATE 2).xlsx
+++ b/output/bkg pending - ICD LKT - Esco Ladkrabang (GATE 2).xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>202610101500</t>
+          <t>202610100500</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">

--- a/output/bkg pending - ICD LKT - Esco Ladkrabang (GATE 2).xlsx
+++ b/output/bkg pending - ICD LKT - Esco Ladkrabang (GATE 2).xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>202610100500</t>
+          <t>202610101500</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
